--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488289_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488289_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.592</v>
+        <v>1.2662</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6008</v>
+        <v>1.2662</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0088</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.1173</v>
+        <v>1.2662</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0852</v>
+        <v>0.6441</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.2025</v>
+        <v>0.6221</v>
       </c>
       <c r="J2" t="n">
-        <v>1.235</v>
+        <v>1.2662</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1413</v>
+        <v>0.6441</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0936</v>
+        <v>0.6221</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.3522</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0561</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2961</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.118</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9424</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1756</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2662</v>
+        <v>0.2932</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2662</v>
+        <v>1.5236</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1.2304</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2662</v>
+        <v>-2.1173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6441</v>
+        <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6221</v>
+        <v>-2.2025</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2662</v>
+        <v>1.235</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6441</v>
+        <v>1.1413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6221</v>
+        <v>0.0936</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-3.3522</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.0561</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-2.2961</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.8192</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.8652</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9825</v>
+        <v>-0.9135</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7312</v>
+        <v>1.4718</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7137</v>
+        <v>-2.3853</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.2384</v>
+        <v>-1.6362</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.3166</v>
+        <v>-0.4689</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9218</v>
+        <v>-1.1674</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4632</v>
+        <v>3.1661</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1386</v>
+        <v>1.1849</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6755</v>
+        <v>1.9812</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7752</v>
+        <v>-4.8024</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.178</v>
+        <v>-1.6538</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5973</v>
+        <v>-3.1485</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6676</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R4" t="n">
         <v>2.594</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2728</v>
+        <v>-0.0544</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6031</v>
+        <v>0.4381</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3303</v>
+        <v>-0.4925</v>
       </c>
       <c r="V4" t="n">
+        <v>1.8888</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.5733</v>
+      </c>
+      <c r="X4" t="n">
         <v>0.3155</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.5177</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.2022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2812</v>
+        <v>-1.0654</v>
       </c>
       <c r="E5" t="n">
-        <v>1.178</v>
+        <v>0.613</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4591</v>
+        <v>-1.6785</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6362</v>
+        <v>-5.8536</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4689</v>
+        <v>-1.8506</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1674</v>
+        <v>-4.003</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1661</v>
+        <v>-1.5123</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1849</v>
+        <v>-0.3737</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9812</v>
+        <v>-1.1386</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.8024</v>
+        <v>-4.3412</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6538</v>
+        <v>-1.4768</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.1485</v>
+        <v>-2.8644</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>2.594</v>
+        <v>2.7793</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.422</v>
+        <v>-0.5263</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1443</v>
+        <v>-0.0948</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5663</v>
+        <v>-0.4315</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8888</v>
+        <v>3.4616</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5733</v>
+        <v>3.1466</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3155</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9714</v>
+        <v>-1.3753</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2683</v>
+        <v>1.5354</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7031</v>
+        <v>-2.9107</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.8536</v>
+        <v>-3.2384</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8506</v>
+        <v>-2.3166</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.003</v>
+        <v>-0.9218</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5123</v>
+        <v>-0.4632</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3737</v>
+        <v>-1.1386</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1386</v>
+        <v>0.6755</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.3412</v>
+        <v>-2.7752</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4768</v>
+        <v>-1.178</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.8644</v>
+        <v>-1.5973</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7793</v>
+        <v>2.594</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4323</v>
+        <v>-0.12</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9762</v>
+        <v>0.4073</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4562</v>
+        <v>-0.5273</v>
       </c>
       <c r="V6" t="n">
-        <v>3.4616</v>
+        <v>0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>3.1466</v>
+        <v>2.5177</v>
       </c>
       <c r="X6" t="n">
-        <v>0.315</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1083</v>
+        <v>-1.7647</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1713</v>
+        <v>-0.9755</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9369</v>
+        <v>-0.7892</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9879</v>
@@ -1000,13 +1000,13 @@
         <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3057</v>
+        <v>0.0379</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0321</v>
+        <v>0.1156</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1854</v>
+        <v>-1.8446</v>
       </c>
       <c r="E8" t="n">
-        <v>0.448</v>
+        <v>1.1335</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6335</v>
+        <v>-2.9782</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2439</v>
@@ -1078,13 +1078,13 @@
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0707</v>
+        <v>0.2701</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3071</v>
+        <v>0.3784</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2365</v>
+        <v>-0.1082</v>
       </c>
       <c r="V8" t="n">
         <v>-0.315</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3673</v>
+        <v>-3.7087</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4923</v>
+        <v>-1.0799</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.875</v>
+        <v>-2.6287</v>
       </c>
       <c r="G9" t="n">
         <v>-2.581</v>
@@ -1156,13 +1156,13 @@
         <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.2568</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8344</v>
+        <v>0.2469</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7499</v>
+        <v>-0.5036</v>
       </c>
       <c r="V9" t="n">
         <v>-0.315</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4908</v>
+        <v>-4.0979</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2567</v>
+        <v>-2.0608</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2341</v>
+        <v>-2.0371</v>
       </c>
       <c r="G10" t="n">
         <v>-5.8694</v>
@@ -1234,13 +1234,13 @@
         <v>2.4087</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0476</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0161</v>
+        <v>0.1797</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0314</v>
+        <v>-0.8344</v>
       </c>
       <c r="V10" t="n">
         <v>0.9439</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7057</v>
+        <v>-5.0235</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7297</v>
+        <v>-2.1214</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.976</v>
+        <v>-2.9021</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0028</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9085</v>
+        <v>0.5907</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8344</v>
+        <v>0.4427</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0741</v>
+        <v>0.148</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5733</v>
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.2344</v>
+        <v>-18.2342</v>
       </c>
       <c r="E12" t="n">
         <v>1.3059</v>
@@ -1366,7 +1366,7 @@
         <v>2.3133</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8554999999999999</v>
+        <v>0.8555000000000004</v>
       </c>
       <c r="L12" t="n">
         <v>1.4578</v>
@@ -1381,7 +1381,7 @@
         <v>-19.3519</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.7493</v>
@@ -1390,16 +1390,16 @@
         <v>15.7493</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1055999999999998</v>
+        <v>0.1057000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7856</v>
+        <v>2.7858</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.68</v>
+        <v>-2.6799</v>
       </c>
       <c r="V12" t="n">
-        <v>6.924199999999999</v>
+        <v>6.924200000000001</v>
       </c>
       <c r="W12" t="n">
         <v>11.9564</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9564</v>
+        <v>7.571</v>
       </c>
       <c r="E13" t="n">
-        <v>7.8488</v>
+        <v>7.653</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1075</v>
+        <v>-0.082</v>
       </c>
       <c r="G13" t="n">
         <v>4.9556</v>
@@ -1468,13 +1468,13 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.519</v>
+        <v>0.1337</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3967</v>
+        <v>0.2009</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1223</v>
+        <v>-0.0672</v>
       </c>
       <c r="V13" t="n">
         <v>0.6289</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.057</v>
+        <v>6.4446</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9396</v>
+        <v>6.0168</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1174</v>
+        <v>0.4278</v>
       </c>
       <c r="G14" t="n">
         <v>6.9558</v>
@@ -1546,13 +1546,13 @@
         <v>2.4087</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3065</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.2229</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4522</v>
+        <v>-0.1418</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8894</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6067</v>
+        <v>3.6639</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2955</v>
+        <v>4.1976</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6888</v>
+        <v>-0.5337</v>
       </c>
       <c r="G15" t="n">
         <v>4.2348</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.093</v>
+        <v>-0.0358</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4004</v>
+        <v>0.3025</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4934</v>
+        <v>-0.3383</v>
       </c>
       <c r="V15" t="n">
         <v>-2.2027</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0696</v>
+        <v>2.4568</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2808</v>
+        <v>0.3994</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7888</v>
+        <v>2.0574</v>
       </c>
       <c r="G16" t="n">
         <v>2.3034</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8779</v>
+        <v>0.2652</v>
       </c>
       <c r="T16" t="n">
-        <v>1.159</v>
+        <v>0.2776</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2811</v>
+        <v>-0.0125</v>
       </c>
       <c r="V16" t="n">
         <v>0.6294</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4484</v>
+        <v>1.3774</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5848</v>
+        <v>2.3257</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1364</v>
+        <v>-0.9483</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9052</v>
+        <v>4.2834</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4921</v>
+        <v>2.1651</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4131</v>
+        <v>2.1183</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7885</v>
+        <v>4.964</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1758</v>
+        <v>2.1854</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6127</v>
+        <v>2.7786</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1167</v>
+        <v>-0.6805</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3163</v>
+        <v>-0.0203</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1996</v>
+        <v>-0.6603</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3706</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0382</v>
+        <v>-5.0027</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1164</v>
+        <v>0.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8344</v>
+        <v>0.7912</v>
       </c>
       <c r="U17" t="n">
-        <v>0.282</v>
+        <v>-0.4912</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.2027</v>
+        <v>0.3144</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2027</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4309</v>
+        <v>1.1626</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2566</v>
+        <v>1.193</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1743</v>
+        <v>-0.0304</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5525</v>
+        <v>2.9052</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0104</v>
+        <v>0.4921</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4578</v>
+        <v>2.4131</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.707</v>
+        <v>2.7885</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4949</v>
+        <v>0.1758</v>
       </c>
       <c r="L18" t="n">
-        <v>0.788</v>
+        <v>2.6127</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1544</v>
+        <v>0.1167</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4846</v>
+        <v>0.3163</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3301</v>
+        <v>-0.1996</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1687</v>
+        <v>0.8307</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7609</v>
+        <v>0.4427</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4079</v>
+        <v>0.388</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3144</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.968</v>
+        <v>0.4442</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4236</v>
+        <v>-0.2255</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4557</v>
+        <v>0.6697</v>
       </c>
       <c r="G19" t="n">
-        <v>4.2834</v>
+        <v>1.1943</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1651</v>
+        <v>-0.231</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1183</v>
+        <v>1.4252</v>
       </c>
       <c r="J19" t="n">
-        <v>4.964</v>
+        <v>1.0514</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1854</v>
+        <v>0.21</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7786</v>
+        <v>0.8414</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6805</v>
+        <v>0.1429</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0203</v>
+        <v>-0.441</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6603</v>
+        <v>0.5839</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.5205</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.0027</v>
+        <v>-2.9646</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1094</v>
+        <v>-0.138</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8891</v>
+        <v>0.1144</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9986</v>
+        <v>-0.2525</v>
       </c>
       <c r="V19" t="n">
         <v>0.3144</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5757</v>
+        <v>0.336</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0089</v>
+        <v>-0.7227</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4332</v>
+        <v>1.0587</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1943</v>
+        <v>-0.5525</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.231</v>
+        <v>-1.0104</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4252</v>
+        <v>0.4578</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0514</v>
+        <v>-0.707</v>
       </c>
       <c r="K20" t="n">
-        <v>0.21</v>
+        <v>-1.4949</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8414</v>
+        <v>0.788</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1429</v>
+        <v>0.1544</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.441</v>
+        <v>0.4846</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5839</v>
+        <v>-0.3301</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9646</v>
+        <v>-1.1117</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.158</v>
+        <v>1.0738</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.669</v>
+        <v>0.7816</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.489</v>
+        <v>0.2922</v>
       </c>
       <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.3144</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.5733</v>
-      </c>
       <c r="X20" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.276</v>
+        <v>-0.7674</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0118</v>
+        <v>-0.5194</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2642</v>
+        <v>-0.248</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2199</v>
+        <v>-0.3428</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2199</v>
+        <v>-0.3441</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0429</v>
+        <v>-0.0241</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0429</v>
+        <v>0.4509</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.475</v>
       </c>
       <c r="M21" t="n">
-        <v>0.177</v>
+        <v>-0.3187</v>
       </c>
       <c r="N21" t="n">
-        <v>0.177</v>
+        <v>-0.795</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.4763</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1079</v>
+        <v>-0.5189</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0547</v>
+        <v>-0.3099</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0532</v>
+        <v>-0.2089</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5733</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. NEWSON</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7186</v>
+        <v>-1.2439</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0597</v>
+        <v>-0.0118</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6588000000000001</v>
+        <v>-1.2321</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8929</v>
+        <v>0.2199</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6424</v>
+        <v>0.2199</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2505</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3797</v>
+        <v>0.0429</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.0429</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1872</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5131</v>
+        <v>0.177</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4377</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5292</v>
+        <v>-0.0759</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.383</v>
+        <v>-0.0547</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1462</v>
+        <v>-0.0211</v>
       </c>
       <c r="V22" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0005</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>X. NEWSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7323</v>
+        <v>-1.2524</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.009</v>
+        <v>-0.766</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.4865</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3428</v>
+        <v>-0.8929</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3441</v>
+        <v>-0.6424</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0012</v>
+        <v>-0.2505</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0241</v>
+        <v>-0.3797</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4509</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.475</v>
+        <v>0.1872</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3187</v>
+        <v>-0.5131</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.795</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4763</v>
+        <v>-0.4377</v>
       </c>
       <c r="P23" t="n">
-        <v>1.6676</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4838</v>
+        <v>-0.0631</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7996</v>
+        <v>-0.0892</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6842</v>
+        <v>0.0261</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5733</v>
+        <v>0.63</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5733</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.2344</v>
+        <v>20.1928</v>
       </c>
       <c r="E24" t="n">
-        <v>19.5403</v>
+        <v>19.5401</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.306</v>
+        <v>0.6526000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>25.2642</v>
       </c>
       <c r="H24" t="n">
-        <v>7.3699</v>
+        <v>7.369899999999999</v>
       </c>
       <c r="I24" t="n">
         <v>17.8941</v>
@@ -2311,13 +2311,13 @@
         <v>-2.3133</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8556000000000001</v>
+        <v>-0.8556</v>
       </c>
       <c r="O24" t="n">
         <v>-1.4577</v>
       </c>
       <c r="P24" t="n">
-        <v>9.999999999910081e-05</v>
+        <v>9.999999999898979e-05</v>
       </c>
       <c r="Q24" t="n">
         <v>-15.7493</v>
@@ -2326,13 +2326,13 @@
         <v>15.7495</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1057999999999995</v>
+        <v>1.8528</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6799</v>
+        <v>2.68</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.7857</v>
+        <v>-0.8272</v>
       </c>
       <c r="V24" t="n">
         <v>-6.9243</v>
